--- a/TS4_mapping.xlsx
+++ b/TS4_mapping.xlsx
@@ -573,8 +573,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>64265166440004</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -585,8 +591,16 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>fiber_check-parse_cpo_data_collect_results-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -617,8 +631,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>64265166440005</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -629,8 +649,16 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>cpld_revision-bmc_cpld_fu_interface_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -661,8 +689,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>64265166440003</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -673,7 +707,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -705,8 +743,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>64265166440001</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -717,8 +761,16 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>initial_setup-mft_revision-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -749,8 +801,14 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>64265166440002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -761,8 +819,16 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>cpld_revision-bmc_cpld_fu_interface_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>

--- a/TS4_mapping.xlsx
+++ b/TS4_mapping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,38 +673,16 @@
       <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TS4</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>64265166010010</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>64265166440003</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>DEV032683</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
@@ -712,7 +690,11 @@
           <t>AOT</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -733,10 +715,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>64265166010009</v>
+        <v>64265166010010</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -744,14 +726,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>64265166440001</v>
+        <v>64265166440003</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>64265165910004</v>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -766,11 +750,7 @@
           <t>AOT</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>initial_setup-mft_revision-FAIL-MEASUREMENT;</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -791,10 +771,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>64265166010008</v>
+        <v>64265166010009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -802,7 +782,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>64265166440002</v>
+        <v>64265166440001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -826,7 +806,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>cpld_revision-bmc_cpld_fu_interface_test-FAIL-MEASUREMENT;</t>
+          <t>initial_setup-mft_revision-FAIL-MEASUREMENT;</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -842,6 +822,102 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>laser_tests_prerequisites-create_mst_devices_els-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TS4</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>64265166010008</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>64265166440002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>64265165910005</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DEV032683</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>AOT</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>cpld_revision-bmc_cpld_fu_interface_test-FAIL-MEASUREMENT;</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
